--- a/static/excel/NFLX_model.xlsx
+++ b/static/excel/NFLX_model.xlsx
@@ -7316,11 +7316,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>375729.684</v>
+        <v>373076.88</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $89.23</t>
+          <t>FMP marketCap  |  price $88.6</t>
         </is>
       </c>
     </row>
@@ -7402,11 +7402,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0467</v>
+        <v>0.0457</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-19</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0467</v>
+        <v>0.0457</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7677,11 +7677,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0521</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.67% + spread 0.54%</t>
+          <t>Rf 4.57% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0519</v>
+        <v>0.0514</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
@@ -7772,16 +7772,16 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B44" s="55">
-        <f>B8*B28+B9*B37*(1-B41)</f>
+        <f>MAX(0.085, B8*B28+B9*B37*(1-B41))</f>
         <v/>
       </c>
       <c r="C44" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="B61" s="111" t="n">
-        <v>89.20999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="C61" s="103" t="n"/>
       <c r="D61" s="103" t="n"/>
@@ -10026,7 +10026,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — NFLX  |  Master Prompt v2  |  22 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — NFLX  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="D22" s="129" t="inlineStr">
         <is>
-          <t>Current 36.1x  |  5yr avg 40.2x  |  DCF-implied 55.4x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.53 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=7.12]  PEG≈285.61 (trailing_pe=36.1x / rev_cagr=13%, revenue proxy)</t>
+          <t>Current 36.1x  |  5yr avg 40.2x  |  DCF-implied 56.2x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.53 | fwd_pe=24.9x→10.00 | abs=1.5 → blended 40/40/20=7.71]  PEG=67.20 (fwd_pe=24.9x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="130" t="inlineStr">
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="F22" s="131" t="n">
-        <v>7.12</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G22" s="132">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="H22" s="133" t="inlineStr">
         <is>
-          <t>Current 36.1x  |  5yr avg 40.2x  |  DCF-implied 55.4x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.53 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=7.12]  PEG≈285.61 (trailing_pe=36.1x / rev_cagr=13%, revenue proxy)</t>
+          <t>Current 36.1x  |  5yr avg 40.2x  |  DCF-implied 56.2x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.53 | fwd_pe=24.9x→10.00 | abs=1.5 → blended 40/40/20=7.71]  PEG=67.20 (fwd_pe=24.9x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="D23" s="129" t="inlineStr">
         <is>
-          <t>Current 41.9x  |  5yr avg 52.3x  |  DCF-implied 64.3x [ref only — not used as benchmark]  [-20% vs benchmark]  [trail=9.98 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=8.29]  [fcf_yield=2.4% vs rf=4.7%  spread=-2.3%→modifier=-0.50]</t>
+          <t>Current 41.9x  |  5yr avg 52.3x  |  DCF-implied 65.2x [ref only — not used as benchmark]  [-20% vs benchmark]  [trail=9.98 | fwd_pfcf=34.8x→10.00 | abs=1.5 → blended 40/40/20=8.29]  [fcf_yield=2.4% vs rf=4.6%  spread=-2.2%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="130" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="H23" s="133" t="inlineStr">
         <is>
-          <t>Current 41.9x  |  5yr avg 52.3x  |  DCF-implied 64.3x [ref only — not used as benchmark]  [-20% vs benchmark]  [trail=9.98 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=8.29]  [fcf_yield=2.4% vs rf=4.7%  spread=-2.3%→modifier=-0.50]</t>
+          <t>Current 41.9x  |  5yr avg 52.3x  |  DCF-implied 65.2x [ref only — not used as benchmark]  [-20% vs benchmark]  [trail=9.98 | fwd_pfcf=34.8x→10.00 | abs=1.5 → blended 40/40/20=8.29]  [fcf_yield=2.4% vs rf=4.6%  spread=-2.2%→modifier=-0.50]</t>
         </is>
       </c>
     </row>

--- a/static/excel/NFLX_model.xlsx
+++ b/static/excel/NFLX_model.xlsx
@@ -7402,11 +7402,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7616,25 +7616,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0507</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A3CAEY — A</t>
         </is>
       </c>
     </row>
@@ -7677,11 +7679,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.54%</t>
+          <t>Rf 4.56% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7707,11 +7709,11 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0514</v>
+        <v>0.0511</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10028,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — NFLX  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — NFLX  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10545,7 @@
       </c>
       <c r="D22" s="129" t="inlineStr">
         <is>
-          <t>Current 36.1x  |  5yr avg 40.2x  |  DCF-implied 56.2x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.53 | fwd_pe=24.9x→10.00 | abs=1.5 → blended 40/40/20=7.71]  PEG=67.20 (fwd_pe=24.9x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 24.9x (scoring basis)  |  5yr avg 39.4x  |  DCF-implied 56.4x [ref only — not used as benchmark]  [-37% vs benchmark]  [trail=10.00 | fwd_pe=24.9x→10.00 | abs=7.0 → blended 40/40/20=9.40]  PEG=67.20 (fwd_pe=24.9x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="130" t="inlineStr">
@@ -10552,7 +10554,7 @@
         </is>
       </c>
       <c r="F22" s="131" t="n">
-        <v>8.210000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="G22" s="132">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10560,7 +10562,7 @@
       </c>
       <c r="H22" s="133" t="inlineStr">
         <is>
-          <t>Current 36.1x  |  5yr avg 40.2x  |  DCF-implied 56.2x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.53 | fwd_pe=24.9x→10.00 | abs=1.5 → blended 40/40/20=7.71]  PEG=67.20 (fwd_pe=24.9x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 24.9x (scoring basis)  |  5yr avg 39.4x  |  DCF-implied 56.4x [ref only — not used as benchmark]  [-37% vs benchmark]  [trail=10.00 | fwd_pe=24.9x→10.00 | abs=7.0 → blended 40/40/20=9.40]  PEG=67.20 (fwd_pe=24.9x / eps_growth=37%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10582,7 @@
       </c>
       <c r="D23" s="129" t="inlineStr">
         <is>
-          <t>Current 41.9x  |  5yr avg 52.3x  |  DCF-implied 65.2x [ref only — not used as benchmark]  [-20% vs benchmark]  [trail=9.98 | fwd_pfcf=34.8x→10.00 | abs=1.5 → blended 40/40/20=8.29]  [fcf_yield=2.4% vs rf=4.6%  spread=-2.2%→modifier=-0.50]</t>
+          <t>Current 41.9x  |  5yr avg 50.2x  |  DCF-implied 65.5x [ref only — not used as benchmark]  [-16% vs benchmark]  [trail=9.43 | fwd_pfcf=34.8x→10.00 | abs=1.5 → blended 40/40/20=8.07]  [fcf_yield=2.4% vs rf=4.6%  spread=-2.2%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="130" t="inlineStr">
@@ -10589,7 +10591,7 @@
         </is>
       </c>
       <c r="F23" s="131" t="n">
-        <v>7.79</v>
+        <v>7.57</v>
       </c>
       <c r="G23" s="132">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10597,7 +10599,7 @@
       </c>
       <c r="H23" s="133" t="inlineStr">
         <is>
-          <t>Current 41.9x  |  5yr avg 52.3x  |  DCF-implied 65.2x [ref only — not used as benchmark]  [-20% vs benchmark]  [trail=9.98 | fwd_pfcf=34.8x→10.00 | abs=1.5 → blended 40/40/20=8.29]  [fcf_yield=2.4% vs rf=4.6%  spread=-2.2%→modifier=-0.50]</t>
+          <t>Current 41.9x  |  5yr avg 50.2x  |  DCF-implied 65.5x [ref only — not used as benchmark]  [-16% vs benchmark]  [trail=9.43 | fwd_pfcf=34.8x→10.00 | abs=1.5 → blended 40/40/20=8.07]  [fcf_yield=2.4% vs rf=4.6%  spread=-2.2%→modifier=-0.50]</t>
         </is>
       </c>
     </row>
